--- a/Données/week.xlsx
+++ b/Données/week.xlsx
@@ -437,7 +437,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
